--- a/frontend/public/wbs_template.xlsx
+++ b/frontend/public/wbs_template.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -516,10 +516,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,20 +585,15 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>進捗率</t>
+          <t>状態</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>状態</t>
+          <t>先行タスク</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>先行タスク</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -646,16 +640,13 @@
           <t>2026/09/25</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -686,28 +677,25 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026/09/21</t>
+          <t>2026/09/26</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026/10/02</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>業務ヒアリング</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>業務ヒアリング</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>山田の作業完了後</t>
         </is>
@@ -725,7 +713,6 @@
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="6" t="n"/>
@@ -739,7 +726,6 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="6" t="n"/>
@@ -753,7 +739,6 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="6" t="n"/>
@@ -767,7 +752,6 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -781,7 +765,6 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="6" t="n"/>
@@ -795,7 +778,6 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="6" t="n"/>
@@ -809,7 +791,6 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="6" t="n"/>
@@ -823,7 +804,6 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="6" t="n"/>
@@ -837,7 +817,6 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="6" t="n"/>
@@ -851,7 +830,6 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="6" t="n"/>
@@ -865,7 +843,6 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="6" t="n"/>
@@ -879,7 +856,6 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="6" t="n"/>
@@ -893,7 +869,6 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="6" t="n"/>
@@ -907,7 +882,6 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="6" t="n"/>
@@ -921,7 +895,6 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="6" t="n"/>
@@ -935,7 +908,6 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="6" t="n"/>
@@ -949,7 +921,6 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="6" t="n"/>
@@ -963,7 +934,6 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="6" t="n"/>
@@ -977,7 +947,6 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="6" t="n"/>
@@ -991,7 +960,6 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="6" t="n"/>
@@ -1005,7 +973,6 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="6" t="n"/>
@@ -1019,7 +986,6 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="6" t="n"/>
@@ -1033,7 +999,6 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="6" t="n"/>
@@ -1047,7 +1012,6 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="6" t="n"/>
@@ -1061,7 +1025,6 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="6" t="n"/>
@@ -1075,7 +1038,6 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="6" t="n"/>
@@ -1089,7 +1051,6 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="6" t="n"/>
@@ -1103,7 +1064,6 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="6" t="n"/>
@@ -1117,7 +1077,6 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="6" t="n"/>
@@ -1131,7 +1090,6 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="6" t="n"/>
@@ -1145,7 +1103,6 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="6" t="n"/>
@@ -1159,7 +1116,6 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="6" t="n"/>
@@ -1173,7 +1129,6 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
-      <c r="L40" s="6" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="6" t="n"/>
@@ -1187,7 +1142,6 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="6" t="n"/>
@@ -1201,7 +1155,6 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="6" t="n"/>
@@ -1215,7 +1168,6 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="6" t="n"/>
@@ -1229,7 +1181,6 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="6" t="n"/>
@@ -1243,7 +1194,6 @@
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
-      <c r="L45" s="6" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="6" t="n"/>
@@ -1257,7 +1207,6 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="6" t="n"/>
@@ -1271,7 +1220,6 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
-      <c r="L47" s="6" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="6" t="n"/>
@@ -1285,7 +1233,6 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="6" t="n"/>
@@ -1299,7 +1246,6 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="6" t="n"/>
@@ -1313,7 +1259,6 @@
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="6" t="n"/>
@@ -1327,7 +1272,6 @@
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="6" t="n"/>
@@ -1341,7 +1285,6 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="6" t="n"/>
@@ -1355,7 +1298,6 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="6" t="n"/>
@@ -1369,7 +1311,6 @@
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="6" t="n"/>
@@ -1383,7 +1324,6 @@
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="6" t="n"/>
@@ -1397,7 +1337,6 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="6" t="n"/>
@@ -1411,16 +1350,11 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
-      <c r="L57" s="6" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation sqref="J8:J57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="状態" prompt="未着手 / 進行中 / 完了 / 保留 から選んでください。空欄なら進捗率から自動判定します。" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="I8:I57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="状態" prompt="未着手 / 進行中 / 完了 / 保留 から選んでください。空欄なら未着手として扱います。" type="list">
       <formula1>"未着手,進行中,完了,保留"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I8:I57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="0〜100で入れてください" error="進捗率は0〜100の数字で入力してください。" promptTitle="進捗率" prompt="0〜100の数字で入れてください（未着手なら空欄か0）。" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
     </dataValidation>
     <dataValidation sqref="G8:G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付を入れてください" error="2026/10/31 のような日付で入力してください。" promptTitle="開始予定日" prompt="2026/10/31 のような日付で入れてください。分からなければ空欄で構いません。" type="date" operator="greaterThan">
       <formula1>DATE(2000,1,1)</formula1>
@@ -1610,14 +1544,14 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>・進捗率 … 0〜100の数字。未着手なら空欄か0。</t>
+          <t>・状態 … 未着手 / 進行中 / 完了 / 保留 から選択。空欄なら未着手として扱います。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>・状態 … 未着手 / 進行中 / 完了 / 保留 から選択。空欄なら進捗率から自動で判定します。</t>
+          <t xml:space="preserve">　（％での進捗率は書かなくて構いません。必要になったらAI PMOの画面で入れられます）</t>
         </is>
       </c>
     </row>
